--- a/product_selector_out/STM32G0 series.xlsx
+++ b/product_selector_out/STM32G0 series.xlsx
@@ -8508,7 +8508,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23223,7 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24858,7 +24858,7 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25185,7 +25185,7 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25839,7 +25839,7 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -30417,7 +30417,7 @@
       </c>
       <c r="BM101" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -31725,7 +31725,7 @@
       </c>
       <c r="BM105" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -32052,7 +32052,7 @@
       </c>
       <c r="BM106" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -41255,9 +41255,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -41475,14 +41475,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY34" s="8" t="inlineStr">
@@ -41555,9 +41555,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41909,9 +41909,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -42129,14 +42129,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY36" s="8" t="inlineStr">
@@ -42209,9 +42209,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42890,9 +42890,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -43110,14 +43110,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY39" s="8" t="inlineStr">
@@ -43190,9 +43190,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43871,9 +43871,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -44091,14 +44091,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY42" s="8" t="inlineStr">
@@ -44171,9 +44171,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44525,9 +44525,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -44745,14 +44745,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY44" s="8" t="inlineStr">
@@ -44825,9 +44825,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44852,9 +44852,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -45072,14 +45072,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY45" s="8" t="inlineStr">
@@ -45152,9 +45152,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45506,9 +45506,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -45726,14 +45726,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY47" s="8" t="inlineStr">
@@ -45806,9 +45806,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -47795,9 +47795,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -48015,14 +48015,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY54" s="8" t="inlineStr">
@@ -48095,9 +48095,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49757,9 +49757,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -49977,14 +49977,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY60" s="8" t="inlineStr">
@@ -50057,9 +50057,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50084,9 +50084,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -50304,14 +50304,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY61" s="8" t="inlineStr">
@@ -50384,9 +50384,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51065,9 +51065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -51285,14 +51285,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY64" s="8" t="inlineStr">
@@ -51365,9 +51365,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51392,9 +51392,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -51612,14 +51612,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY65" s="8" t="inlineStr">
@@ -51692,9 +51692,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52046,9 +52046,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -52266,14 +52266,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY67" s="8" t="inlineStr">
@@ -52346,9 +52346,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52373,9 +52373,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -52593,14 +52593,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY68" s="8" t="inlineStr">
@@ -52673,9 +52673,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54335,9 +54335,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -54555,14 +54555,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY74" s="8" t="inlineStr">
@@ -54635,9 +54635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54989,9 +54989,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -55209,14 +55209,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY76" s="8" t="inlineStr">
@@ -55289,9 +55289,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55970,9 +55970,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -56190,14 +56190,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY79" s="8" t="inlineStr">
@@ -56270,9 +56270,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -56951,9 +56951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -57171,14 +57171,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW82" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY82" s="8" t="inlineStr">
@@ -57251,9 +57251,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57278,9 +57278,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -57498,14 +57498,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY83" s="8" t="inlineStr">
@@ -57578,9 +57578,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57605,9 +57605,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -57825,14 +57825,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW84" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY84" s="8" t="inlineStr">
@@ -57905,9 +57905,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57932,9 +57932,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -58152,14 +58152,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW85" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY85" s="8" t="inlineStr">
@@ -58232,9 +58232,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -58259,9 +58259,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -58479,14 +58479,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY86" s="8" t="inlineStr">
@@ -58559,9 +58559,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -58586,9 +58586,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -58806,14 +58806,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW87" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY87" s="8" t="inlineStr">
@@ -58886,9 +58886,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -63164,9 +63164,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
@@ -63229,14 +63229,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R101" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S101" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R101" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S101" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T101" s="8" t="inlineStr">
@@ -63394,9 +63394,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY101" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ101" s="6" t="inlineStr">
@@ -63464,9 +63464,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM101" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -64472,9 +64472,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -64537,14 +64537,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R105" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S105" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R105" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S105" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T105" s="6" t="inlineStr">
@@ -64702,9 +64702,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY105" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY105" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ105" s="6" t="inlineStr">
@@ -64772,9 +64772,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM105" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM105" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -64799,9 +64799,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
@@ -64864,14 +64864,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R106" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S106" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R106" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S106" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T106" s="6" t="inlineStr">
@@ -65029,9 +65029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY106" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY106" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ106" s="6" t="inlineStr">
@@ -65099,9 +65099,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM106" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM106" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -66428,7 +66428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -66477,7 +66477,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66565,7 +66565,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66609,7 +66609,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66653,7 +66653,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66697,7 +66697,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66741,7 +66741,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66785,7 +66785,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66829,7 +66829,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66873,7 +66873,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66917,7 +66917,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66961,7 +66961,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67005,7 +67005,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67049,7 +67049,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67093,7 +67093,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67137,7 +67137,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67181,7 +67181,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67225,7 +67225,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67269,7 +67269,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67313,7 +67313,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67357,7 +67357,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67401,7 +67401,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67430,7 +67430,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G0B1KB</t>
+          <t>STM32G0B1CB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -67445,14 +67445,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G0B1CB</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -67467,19 +67467,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G0C1RE</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -67489,14 +67489,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -67511,14 +67511,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -67540,7 +67540,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -67555,14 +67555,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -67584,7 +67584,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G0C1VE</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -67599,19 +67599,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -67621,19 +67621,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -67643,19 +67643,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -67665,19 +67665,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -67687,19 +67687,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G0B1RB</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -67709,14 +67709,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -67731,14 +67731,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -67760,7 +67760,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G0C1ME</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -67775,19 +67775,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G0C1KE</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -67797,14 +67797,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -67819,14 +67819,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -67848,7 +67848,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G0C1CE</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -67863,19 +67863,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -67885,19 +67885,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -67907,19 +67907,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -67929,19 +67929,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -67951,19 +67951,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -67973,19 +67973,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -67995,19 +67995,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -68017,19 +68017,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -68039,19 +68039,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -68061,19 +68061,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -68083,19 +68083,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -68105,19 +68105,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -68127,19 +68127,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G0B1MC</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -68149,14 +68149,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G0C1CC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -68171,19 +68171,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -68193,19 +68193,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -68215,19 +68215,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -68237,19 +68237,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -68259,19 +68259,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -68281,19 +68281,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -68303,19 +68303,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -68325,19 +68325,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G0C1CC</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -68347,14 +68347,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G0C1KC</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -68369,19 +68369,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G0B1RE</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -68391,14 +68391,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -68413,19 +68413,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -68435,19 +68435,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -68457,19 +68457,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -68479,19 +68479,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G0B1VE</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -68501,14 +68501,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G0B1NE</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -68523,19 +68523,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -68545,19 +68545,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -68567,19 +68567,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G0B1ME</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -68589,14 +68589,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G0B1KC</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -68611,19 +68611,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -68633,19 +68633,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G051F6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -68655,19 +68655,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G051F6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -68677,19 +68677,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G051G6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -68699,19 +68699,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G0B1CC</t>
+          <t>STM32G051G6</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -68721,14 +68721,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G041K6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -68743,14 +68743,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G041K6</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -68772,7 +68772,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G041G6</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -68787,14 +68787,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G041G6</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -68816,7 +68816,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G0B1RC</t>
+          <t>STM32G071EB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -68831,19 +68831,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G071EB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -68853,19 +68853,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G031Y8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -68875,19 +68875,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G0B1VC</t>
+          <t>STM32G031Y8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -68897,14 +68897,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G041Y8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -68919,14 +68919,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G041Y8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -68948,12 +68948,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -68963,19 +68963,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -68985,19 +68985,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32G0B1CE</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -69007,19 +69007,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -69029,19 +69029,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -69051,19 +69051,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -69073,19 +69073,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -69095,19 +69095,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32G0C1RC</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -69117,19 +69117,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32G0B1VB</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -69139,19 +69139,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32G0C1VC</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -69161,19 +69161,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32G0C1MC</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -69183,19 +69183,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32G0B1KE</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -69205,19 +69205,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32G0B1MB</t>
+          <t>STM32G070RB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -69227,19 +69227,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G070RB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -69249,14 +69249,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G070RB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -69271,19 +69271,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -69293,19 +69293,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -69315,19 +69315,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -69337,19 +69337,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -69359,19 +69359,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -69381,14 +69381,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -69410,12 +69410,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G070KB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -69425,19 +69425,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G070KB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -69447,19 +69447,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G070KB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -69469,19 +69469,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -69498,12 +69498,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -69513,19 +69513,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -69535,19 +69535,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -69557,19 +69557,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -69579,19 +69579,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -69601,19 +69601,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -69630,12 +69630,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -69645,19 +69645,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -69667,19 +69667,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -69689,19 +69689,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -69711,19 +69711,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -69733,19 +69733,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -69755,19 +69755,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -69777,19 +69777,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -69799,19 +69799,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -69828,12 +69828,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -69843,19 +69843,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -69865,19 +69865,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -69894,12 +69894,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -69909,19 +69909,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -69930,710 +69930,6 @@
         </is>
       </c>
       <c r="D159" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>STM32G070KB</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>STM32G070KB</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>STM32G0B0KE</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>STM32G0B0KE</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>STM32G0B0KE</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>STM32G030C8</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>STM32G030C8</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>STM32G030C8</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>STM32G0B0CE</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>STM32G0B0CE</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>STM32G0B0CE</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>STM32G030C6</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>STM32G030C6</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>STM32G030C6</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>STM32G0B0RE</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>STM32G0B0RE</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>STM32G0B0RE</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>STM32G0B0VE</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>STM32G0B0VE</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>STM32G0B0VE</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>STM32G050C6</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>STM32G050C6</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>STM32G050C6</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>STM32G050K8</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>STM32G050K8</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>STM32G050K8</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0 series.xlsx
+++ b/product_selector_out/STM32G0 series.xlsx
@@ -8508,7 +8508,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23223,7 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -24858,7 +24858,7 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -25185,7 +25185,7 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -25839,7 +25839,7 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -30417,7 +30417,7 @@
       </c>
       <c r="BM101" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -31725,7 +31725,7 @@
       </c>
       <c r="BM105" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -32052,7 +32052,7 @@
       </c>
       <c r="BM106" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -41255,9 +41255,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -41475,14 +41475,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY34" s="8" t="inlineStr">
@@ -41555,9 +41555,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41909,9 +41909,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -42129,14 +42129,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY36" s="8" t="inlineStr">
@@ -42209,9 +42209,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -42890,9 +42890,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -43110,14 +43110,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY39" s="8" t="inlineStr">
@@ -43190,9 +43190,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -43871,9 +43871,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -44091,14 +44091,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY42" s="8" t="inlineStr">
@@ -44171,9 +44171,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44525,9 +44525,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -44745,14 +44745,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY44" s="8" t="inlineStr">
@@ -44825,9 +44825,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44852,9 +44852,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -45072,14 +45072,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY45" s="8" t="inlineStr">
@@ -45152,9 +45152,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45506,9 +45506,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -45726,14 +45726,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY47" s="8" t="inlineStr">
@@ -45806,9 +45806,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -47795,9 +47795,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -48015,14 +48015,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY54" s="8" t="inlineStr">
@@ -48095,9 +48095,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -49757,9 +49757,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -49977,14 +49977,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX60" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY60" s="8" t="inlineStr">
@@ -50057,9 +50057,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -50084,9 +50084,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -50304,14 +50304,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY61" s="8" t="inlineStr">
@@ -50384,9 +50384,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -51065,9 +51065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -51285,14 +51285,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY64" s="8" t="inlineStr">
@@ -51365,9 +51365,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -51392,9 +51392,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -51612,14 +51612,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY65" s="8" t="inlineStr">
@@ -51692,9 +51692,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -52046,9 +52046,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -52266,14 +52266,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY67" s="8" t="inlineStr">
@@ -52346,9 +52346,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -52373,9 +52373,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -52593,14 +52593,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY68" s="8" t="inlineStr">
@@ -52673,9 +52673,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54335,9 +54335,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -54555,14 +54555,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY74" s="8" t="inlineStr">
@@ -54635,9 +54635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54989,9 +54989,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -55209,14 +55209,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY76" s="8" t="inlineStr">
@@ -55289,9 +55289,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55970,9 +55970,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -56190,14 +56190,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY79" s="8" t="inlineStr">
@@ -56270,9 +56270,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -56951,9 +56951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -57171,14 +57171,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY82" s="8" t="inlineStr">
@@ -57251,9 +57251,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -57278,9 +57278,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -57498,14 +57498,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY83" s="8" t="inlineStr">
@@ -57578,9 +57578,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -57605,9 +57605,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -57825,14 +57825,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY84" s="8" t="inlineStr">
@@ -57905,9 +57905,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -57932,9 +57932,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -58152,14 +58152,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY85" s="8" t="inlineStr">
@@ -58232,9 +58232,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -58259,9 +58259,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -58479,14 +58479,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY86" s="8" t="inlineStr">
@@ -58559,9 +58559,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -58586,9 +58586,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -58806,14 +58806,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY87" s="8" t="inlineStr">
@@ -58886,9 +58886,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -63164,9 +63164,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
@@ -63229,14 +63229,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R101" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S101" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R101" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S101" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T101" s="8" t="inlineStr">
@@ -63394,9 +63394,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY101" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AY101" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ101" s="6" t="inlineStr">
@@ -63464,9 +63464,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM101" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM101" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -64472,9 +64472,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -64537,14 +64537,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R105" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S105" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R105" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S105" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T105" s="6" t="inlineStr">
@@ -64702,9 +64702,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY105" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AY105" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ105" s="6" t="inlineStr">
@@ -64772,9 +64772,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM105" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM105" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -64799,9 +64799,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
@@ -64864,14 +64864,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R106" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S106" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R106" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S106" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T106" s="6" t="inlineStr">
@@ -65029,9 +65029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY106" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AY106" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ106" s="6" t="inlineStr">
@@ -65099,9 +65099,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM106" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM106" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -66428,7 +66428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67430,7 +67430,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G0B1CB</t>
+          <t>STM32G0B1KB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -67452,7 +67452,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G0B1CB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -67467,19 +67467,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G0C1RE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -67489,14 +67489,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -67518,7 +67518,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -67540,7 +67540,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -67562,7 +67562,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -67584,7 +67584,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G0C1VE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -67599,19 +67599,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -67621,19 +67621,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -67643,19 +67643,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -67665,19 +67665,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -67687,19 +67687,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G0B1RB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -67709,14 +67709,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -67738,7 +67738,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -67760,7 +67760,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G0C1ME</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -67775,19 +67775,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G0C1KE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -67797,14 +67797,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -67826,7 +67826,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -67848,7 +67848,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G0C1CE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -67863,19 +67863,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -67885,19 +67885,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -67907,19 +67907,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -67929,19 +67929,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -67951,19 +67951,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -67973,19 +67973,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -67995,19 +67995,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -68017,19 +68017,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -68039,19 +68039,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -68061,19 +68061,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -68083,19 +68083,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -68105,19 +68105,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -68127,19 +68127,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G0B1MC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -68149,14 +68149,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G0C1CC</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -68171,19 +68171,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -68193,19 +68193,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -68215,19 +68215,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -68237,19 +68237,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -68259,19 +68259,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -68281,19 +68281,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -68303,19 +68303,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -68325,19 +68325,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G0C1CC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -68347,14 +68347,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G0C1KC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -68369,19 +68369,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G0B1RE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -68391,14 +68391,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G0B1CC</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -68413,19 +68413,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -68435,19 +68435,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -68457,19 +68457,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -68479,19 +68479,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G0B1VE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -68501,14 +68501,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G0B1NE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -68523,19 +68523,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -68545,19 +68545,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -68567,19 +68567,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G0B1ME</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -68589,14 +68589,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G0B1KC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -68611,19 +68611,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -68633,19 +68633,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -68655,19 +68655,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -68677,19 +68677,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -68699,19 +68699,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -68721,14 +68721,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -68750,7 +68750,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -68772,7 +68772,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -68794,7 +68794,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -68816,7 +68816,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G0B1RC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -68831,19 +68831,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -68853,19 +68853,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -68875,19 +68875,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G0B1VC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -68897,14 +68897,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -68926,7 +68926,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -68948,12 +68948,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -68963,19 +68963,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -68985,19 +68985,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G0B1CE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -69007,19 +69007,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G051F6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -69029,19 +69029,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G051F6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -69051,19 +69051,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G051G6</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -69073,19 +69073,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G051G6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -69095,19 +69095,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G0C1RC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -69117,19 +69117,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G0B1VB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -69139,19 +69139,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G0C1VC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -69161,19 +69161,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G0C1MC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -69183,19 +69183,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G0B1KE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -69205,19 +69205,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G0B1MB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -69227,19 +69227,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G041K6</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -69249,14 +69249,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G041K6</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -69271,19 +69271,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G041G6</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -69293,19 +69293,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G041G6</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -69315,19 +69315,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G071EB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -69337,19 +69337,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G071EB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -69359,19 +69359,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G031Y8</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -69381,14 +69381,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G031Y8</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -69410,12 +69410,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G041Y8</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -69425,19 +69425,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G041Y8</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -69447,19 +69447,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -69469,19 +69469,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -69498,12 +69498,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -69513,19 +69513,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -69535,19 +69535,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -69557,19 +69557,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -69579,19 +69579,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -69601,19 +69601,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -69630,12 +69630,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -69645,19 +69645,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -69667,19 +69667,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -69689,19 +69689,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -69711,19 +69711,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G070RB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -69733,19 +69733,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G070RB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -69755,19 +69755,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G070RB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -69777,19 +69777,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -69799,19 +69799,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -69828,12 +69828,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -69843,19 +69843,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -69865,19 +69865,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32G050F6</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -69894,12 +69894,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32G050F6</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -69909,27 +69909,731 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>STM32G070KB</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>STM32G070KB</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>STM32G070KB</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>STM32G0B0KE</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>STM32G0B0KE</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>STM32G0B0KE</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>STM32G030C8</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>STM32G030C8</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>STM32G030C8</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>STM32G0B0CE</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>STM32G0B0CE</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>STM32G0B0CE</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>STM32G030C6</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>STM32G030C6</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>STM32G030C6</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>STM32G0B0RE</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>STM32G0B0RE</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>STM32G0B0RE</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>STM32G0B0VE</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>STM32G0B0VE</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>STM32G0B0VE</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>STM32G050C6</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>STM32G050C6</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>STM32G050C6</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
           <t>STM32G050F6</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>STM32G050F6</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>STM32G050F6</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
         <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0 series.xlsx
+++ b/product_selector_out/STM32G0 series.xlsx
@@ -8508,7 +8508,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23223,7 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -25839,7 +25839,7 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="BM92" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="BM97" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g070cb.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="BM100" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g070cb.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -41320,14 +41320,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -41475,19 +41475,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="9" t="inlineStr">
+      <c r="AW34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY34" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ34" s="6" t="inlineStr">
@@ -43936,14 +43936,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T42" s="6" t="inlineStr">
@@ -44091,19 +44091,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="9" t="inlineStr">
+      <c r="AW42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY42" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ42" s="6" t="inlineStr">
@@ -47860,14 +47860,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T54" s="6" t="inlineStr">
@@ -48015,19 +48015,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="9" t="inlineStr">
+      <c r="AW54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY54" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY54" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ54" s="6" t="inlineStr">
@@ -50149,14 +50149,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
@@ -50304,19 +50304,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="9" t="inlineStr">
+      <c r="AW61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY61" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY61" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ61" s="6" t="inlineStr">
@@ -51130,14 +51130,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T64" s="6" t="inlineStr">
@@ -51285,19 +51285,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="9" t="inlineStr">
+      <c r="AW64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY64" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ64" s="6" t="inlineStr">
@@ -51457,14 +51457,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -51612,19 +51612,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="9" t="inlineStr">
+      <c r="AW65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY65" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY65" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ65" s="6" t="inlineStr">
@@ -52111,14 +52111,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T67" s="6" t="inlineStr">
@@ -52266,19 +52266,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="9" t="inlineStr">
+      <c r="AW67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY67" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY67" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ67" s="6" t="inlineStr">
@@ -52438,14 +52438,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -52593,19 +52593,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="9" t="inlineStr">
+      <c r="AW68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY68" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ68" s="6" t="inlineStr">
@@ -53419,14 +53419,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -53574,19 +53574,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW71" s="9" t="inlineStr">
+      <c r="AW71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY71" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY71" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ71" s="6" t="inlineStr">
@@ -54400,14 +54400,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
@@ -54555,19 +54555,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="9" t="inlineStr">
+      <c r="AW74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY74" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ74" s="6" t="inlineStr">
@@ -55054,14 +55054,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T76" s="6" t="inlineStr">
@@ -55209,19 +55209,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="9" t="inlineStr">
+      <c r="AW76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY76" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY76" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ76" s="6" t="inlineStr">
@@ -56035,14 +56035,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T79" s="6" t="inlineStr">
@@ -56190,19 +56190,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="9" t="inlineStr">
+      <c r="AW79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY79" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY79" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ79" s="6" t="inlineStr">
@@ -57343,14 +57343,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T83" s="6" t="inlineStr">
@@ -57498,19 +57498,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="9" t="inlineStr">
+      <c r="AW83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY83" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY83" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ83" s="6" t="inlineStr">
@@ -58324,14 +58324,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T86" s="6" t="inlineStr">
@@ -58479,19 +58479,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="9" t="inlineStr">
+      <c r="AW86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY86" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY86" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ86" s="6" t="inlineStr">
@@ -58651,14 +58651,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T87" s="6" t="inlineStr">
@@ -58806,19 +58806,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW87" s="9" t="inlineStr">
+      <c r="AW87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY87" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY87" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ87" s="6" t="inlineStr">
@@ -60221,9 +60221,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -60441,19 +60441,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ92" s="8" t="inlineStr">
@@ -60521,9 +60521,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -61856,9 +61856,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -61921,14 +61921,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R97" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S97" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T97" s="8" t="inlineStr">
@@ -62086,9 +62086,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY97" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ97" s="8" t="inlineStr">
@@ -62156,9 +62156,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -62837,9 +62837,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
@@ -62902,14 +62902,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R100" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S100" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R100" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S100" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T100" s="8" t="inlineStr">
@@ -63067,9 +63067,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY100" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY100" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ100" s="8" t="inlineStr">
@@ -63137,9 +63137,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM100" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM100" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -66428,7 +66428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67435,7 +67435,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -67445,19 +67445,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G0B1CB</t>
+          <t>STM32G0B1KB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -67467,19 +67467,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G0C1RE</t>
+          <t>STM32G0B1KB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -67489,14 +67489,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G0B1CB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -67511,19 +67511,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G0C1RE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -67533,14 +67533,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -67562,7 +67562,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -67584,7 +67584,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G0C1VE</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -67599,19 +67599,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -67621,19 +67621,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G0C1VE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -67643,14 +67643,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -67672,7 +67672,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -67694,7 +67694,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G0B1RB</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -67709,19 +67709,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -67731,19 +67731,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G0B1RB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -67753,19 +67753,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G0C1ME</t>
+          <t>STM32G0B1RB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -67775,19 +67775,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G0C1KE</t>
+          <t>STM32G0B1RB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -67797,14 +67797,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -67826,7 +67826,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -67848,7 +67848,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G0C1CE</t>
+          <t>STM32G0C1ME</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -67870,7 +67870,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G0C1KE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -67885,19 +67885,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -67907,19 +67907,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -67929,19 +67929,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G0C1CE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -67951,14 +67951,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -67980,7 +67980,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -68002,7 +68002,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -68024,7 +68024,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -68046,7 +68046,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -68068,7 +68068,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -68090,7 +68090,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -68112,7 +68112,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -68134,7 +68134,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G0B1MC</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -68149,19 +68149,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -68171,19 +68171,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -68193,19 +68193,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -68215,19 +68215,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G0B1MC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -68237,19 +68237,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G0B1MC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -68259,14 +68259,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G0B1MC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -68281,14 +68281,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -68310,7 +68310,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -68332,7 +68332,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G0C1CC</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -68347,19 +68347,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G0C1KC</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -68369,14 +68369,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G0B1RE</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -68391,19 +68391,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -68413,19 +68413,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -68435,19 +68435,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -68457,19 +68457,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G0C1CC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -68479,14 +68479,14 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G0B1VE</t>
+          <t>STM32G0C1KC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -68508,12 +68508,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G0B1NE</t>
+          <t>STM32G0B1RE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -68523,19 +68523,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G0B1RE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -68545,14 +68545,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G0B1RE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -68567,14 +68567,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G0B1ME</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -68589,19 +68589,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G0B1KC</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -68611,14 +68611,14 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -68640,7 +68640,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -68662,12 +68662,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G0B1VE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -68677,19 +68677,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G0B1VE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -68699,19 +68699,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G0B1CC</t>
+          <t>STM32G0B1VE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -68721,19 +68721,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G0B1NE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -68743,19 +68743,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G0B1NE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -68765,19 +68765,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G0B1NE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -68787,19 +68787,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -68809,19 +68809,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G0B1RC</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -68831,19 +68831,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G0B1ME</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -68853,19 +68853,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G0B1ME</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -68875,19 +68875,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G0B1VC</t>
+          <t>STM32G0B1ME</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -68897,19 +68897,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G0B1KC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -68919,19 +68919,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G0B1KC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -68941,19 +68941,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G0B1KC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -68963,19 +68963,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -68985,19 +68985,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32G0B1CE</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -69007,14 +69007,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -69036,7 +69036,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -69058,12 +69058,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -69073,19 +69073,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -69095,19 +69095,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32G0C1RC</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -69117,14 +69117,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32G0B1VB</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -69139,19 +69139,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32G0C1VC</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -69161,14 +69161,14 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32G0C1MC</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -69183,19 +69183,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32G0B1KE</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -69205,19 +69205,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32G0B1MB</t>
+          <t>STM32G0B1RC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -69227,19 +69227,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G0B1RC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -69249,14 +69249,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G0B1RC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -69271,14 +69271,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -69300,7 +69300,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -69322,12 +69322,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G0B1VC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -69337,19 +69337,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G0B1VC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -69359,19 +69359,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G0B1VC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -69381,19 +69381,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -69403,19 +69403,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -69425,19 +69425,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -69447,19 +69447,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -69469,19 +69469,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G0B1CE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -69491,19 +69491,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32G030J6</t>
+          <t>STM32G0B1CE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -69513,19 +69513,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G0B1CE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -69535,19 +69535,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G051F6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -69557,14 +69557,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32G030F6</t>
+          <t>STM32G051F6</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -69586,12 +69586,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G051G6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -69601,19 +69601,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G051G6</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -69623,19 +69623,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32G050C8</t>
+          <t>STM32G0C1RC</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -69645,14 +69645,14 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G0B1VB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -69674,7 +69674,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G0B1VB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -69696,7 +69696,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32G070CB</t>
+          <t>STM32G0B1VB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -69711,19 +69711,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G0C1VC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -69733,19 +69733,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G0C1MC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -69755,19 +69755,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G0B1KE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -69777,19 +69777,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G0B1KE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -69799,19 +69799,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G0B1KE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -69821,19 +69821,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G0B1MB</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -69843,19 +69843,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G0B1MB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -69865,19 +69865,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G0B1MB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -69887,19 +69887,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G041K6</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -69909,19 +69909,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G041K6</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -69931,19 +69931,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G041G6</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -69953,14 +69953,14 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G041G6</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -69975,19 +69975,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G071EB</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -69997,19 +69997,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G071EB</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -70019,19 +70019,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G031Y8</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -70041,19 +70041,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G031Y8</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -70063,19 +70063,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -70092,12 +70092,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -70107,19 +70107,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030J6</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -70129,19 +70129,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -70151,19 +70151,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -70173,19 +70173,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G030F6</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -70195,19 +70195,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -70224,12 +70224,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -70239,19 +70239,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G050C8</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -70261,19 +70261,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -70290,12 +70290,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -70305,19 +70305,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G070CB</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -70327,19 +70327,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 24. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -70349,19 +70349,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -70371,19 +70371,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -70393,19 +70393,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -70422,12 +70422,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -70437,19 +70437,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -70459,19 +70459,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -70481,19 +70481,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -70503,19 +70503,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -70525,19 +70525,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -70554,12 +70554,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -70569,19 +70569,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32G050F6</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -70591,19 +70591,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32G050F6</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -70613,27 +70613,511 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t>STM32G0B0CE</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>STM32G0B0CE</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>STM32G030C6</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>STM32G030C6</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>STM32G030C6</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>STM32G0B0RE</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>STM32G0B0RE</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>STM32G0B0RE</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>STM32G0B0VE</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>STM32G0B0VE</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>STM32G0B0VE</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>STM32G050C6</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>STM32G050C6</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>STM32G050C6</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
           <t>STM32G050F6</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>STM32G050F6</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>STM32G050F6</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
         <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0 series.xlsx
+++ b/product_selector_out/STM32G0 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM110"/>
+  <dimension ref="A1:BN110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.08203125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b1cb.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -15702,6 +15929,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -18645,6 +18917,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -18972,6 +19249,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -19299,6 +19581,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -19626,6 +19913,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -19953,6 +20245,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -20280,6 +20577,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -20607,6 +20909,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -20934,6 +21241,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -21261,6 +21573,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -21588,6 +21905,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -21915,6 +22237,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -22242,6 +22569,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -22569,6 +22901,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -22896,6 +23233,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -23223,6 +23565,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -23550,6 +23897,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -23877,6 +24229,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -24204,6 +24561,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -24531,6 +24893,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -24858,6 +25225,11 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -25185,6 +25557,11 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -25512,6 +25889,11 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -25839,6 +26221,11 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -26166,6 +26553,11 @@
       </c>
       <c r="BM88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -26493,6 +26885,11 @@
       </c>
       <c r="BM89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -26820,6 +27217,11 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -27147,6 +27549,11 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -27477,6 +27884,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN92" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -27801,6 +28213,11 @@
       </c>
       <c r="BM93" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -28128,6 +28545,11 @@
       </c>
       <c r="BM94" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -28455,6 +28877,11 @@
       </c>
       <c r="BM95" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN95" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
@@ -28782,6 +29209,11 @@
       </c>
       <c r="BM96" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN96" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g070cb.pdf</t>
         </is>
       </c>
@@ -29112,6 +29544,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN97" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -29436,6 +29873,11 @@
       </c>
       <c r="BM98" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN98" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -29763,6 +30205,11 @@
       </c>
       <c r="BM99" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN99" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -30093,6 +30540,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN100" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -30417,6 +30869,11 @@
       </c>
       <c r="BM101" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN101" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -30744,6 +31201,11 @@
       </c>
       <c r="BM102" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN102" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -31071,6 +31533,11 @@
       </c>
       <c r="BM103" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN103" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -31398,6 +31865,11 @@
       </c>
       <c r="BM104" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN104" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -31725,6 +32197,11 @@
       </c>
       <c r="BM105" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN105" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -32052,6 +32529,11 @@
       </c>
       <c r="BM106" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN106" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -32379,6 +32861,11 @@
       </c>
       <c r="BM107" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN107" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
@@ -32706,6 +33193,11 @@
       </c>
       <c r="BM108" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN108" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
@@ -33033,6 +33525,11 @@
       </c>
       <c r="BM109" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN109" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
@@ -33360,12 +33857,17 @@
       </c>
       <c r="BM110" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN110" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -33386,16 +33888,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -33408,6 +33908,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -33427,7 +33928,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -33543,7 +34046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM110"/>
+  <dimension ref="A1:BN110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33611,6 +34114,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33944,6 +34448,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -34039,6 +34548,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -34361,7 +34871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34688,7 +35203,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35015,7 +35535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35342,7 +35867,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35669,7 +36199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35996,7 +36531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36323,7 +36863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36650,7 +37195,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36977,7 +37527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37304,7 +37859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37631,7 +38191,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37958,7 +38523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38285,7 +38855,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38612,7 +39187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38939,7 +39519,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39266,7 +39851,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39593,7 +40183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39920,7 +40515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40247,7 +40847,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40574,7 +41179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40901,7 +41511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41228,7 +41843,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41555,7 +42175,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41882,7 +42507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42209,7 +42839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42536,7 +43171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42863,7 +43503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43190,7 +43835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43517,7 +44167,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43844,7 +44499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44171,7 +44831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44498,7 +45163,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44825,7 +45495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45152,7 +45827,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45479,7 +46159,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45806,7 +46491,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46133,7 +46823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46460,7 +47155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46787,7 +47487,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47114,7 +47819,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47441,7 +48151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47768,7 +48483,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48095,7 +48815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48422,7 +49147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48749,7 +49479,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49076,7 +49811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49403,7 +50143,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49730,7 +50475,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50057,7 +50807,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50384,7 +51139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50711,7 +51471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51038,7 +51803,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51365,7 +52135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51692,7 +52467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52019,7 +52799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52346,7 +53131,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52673,7 +53463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53000,7 +53795,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53327,7 +54127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53654,7 +54459,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53981,7 +54791,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54308,7 +55123,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54635,7 +55455,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54962,7 +55787,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55289,7 +56119,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55616,7 +56451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55943,7 +56783,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56270,7 +57115,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56597,7 +57447,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56924,7 +57779,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57251,7 +58111,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57578,7 +58443,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57905,7 +58775,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58232,7 +59107,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58559,7 +59439,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58886,7 +59771,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59213,7 +60103,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM88" s="6" t="inlineStr">
+      <c r="BM88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59540,7 +60435,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM89" s="6" t="inlineStr">
+      <c r="BM89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59867,7 +60767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
+      <c r="BM90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60194,7 +61099,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM91" s="6" t="inlineStr">
+      <c r="BM91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60526,6 +61436,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -60848,7 +61763,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM93" s="6" t="inlineStr">
+      <c r="BM93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61175,7 +62095,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM94" s="6" t="inlineStr">
+      <c r="BM94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61502,7 +62427,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM95" s="6" t="inlineStr">
+      <c r="BM95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN95" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61829,7 +62759,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM96" s="6" t="inlineStr">
+      <c r="BM96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN96" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62161,6 +63096,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -62483,7 +63423,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM98" s="6" t="inlineStr">
+      <c r="BM98" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN98" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62810,7 +63755,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM99" s="6" t="inlineStr">
+      <c r="BM99" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN99" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63142,6 +64092,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN100" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -63464,7 +64419,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM101" s="6" t="inlineStr">
+      <c r="BM101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN101" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63791,7 +64751,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM102" s="6" t="inlineStr">
+      <c r="BM102" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN102" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -64118,7 +65083,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM103" s="6" t="inlineStr">
+      <c r="BM103" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN103" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -64445,7 +65415,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM104" s="6" t="inlineStr">
+      <c r="BM104" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN104" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -64772,7 +65747,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM105" s="6" t="inlineStr">
+      <c r="BM105" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN105" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -65099,7 +66079,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM106" s="6" t="inlineStr">
+      <c r="BM106" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN106" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -65426,7 +66411,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM107" s="6" t="inlineStr">
+      <c r="BM107" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN107" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -65753,7 +66743,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM108" s="6" t="inlineStr">
+      <c r="BM108" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN108" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -66080,7 +67075,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM109" s="6" t="inlineStr">
+      <c r="BM109" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN109" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -66407,7 +67407,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM110" s="6" t="inlineStr">
+      <c r="BM110" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN110" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -66415,8 +67420,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
